--- a/other/input/AQWMS/swwtp_site_names_matching_table_manual_edit.xlsx
+++ b/other/input/AQWMS/swwtp_site_names_matching_table_manual_edit.xlsx
@@ -549,6 +549,10 @@
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="3.85546875" customWidth="1"/>
+    <col min="7" max="7" width="3.5703125" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
